--- a/output/pdf_financials_xlsx/ACB.xlsx
+++ b/output/pdf_financials_xlsx/ACB.xlsx
@@ -2953,34 +2953,34 @@
         <v>0.736</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.544</v>
+        <v>3.126</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0</v>
+        <v>7.594</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>233.282</v>
+        <v>24.323</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0</v>
+        <v>22.137</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>113.117</v>
+        <v>11.169</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>189.885</v>
+        <v>6.539</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>138.853</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>97.461</v>
+        <v>9.401999999999999</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0</v>
+        <v>0.011215</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.08111</v>
+        <v>0.01112</v>
       </c>
     </row>
     <row r="49">
@@ -3005,16 +3005,18 @@
         <v>5.244</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>3.126</v>
-      </c>
-      <c r="H49" s="3" t="n">
-        <v>7.594</v>
+        <v>193.606</v>
+      </c>
+      <c r="H49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I49" s="3" t="n">
         <v>660.578</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>22.137</v>
+        <v>420.739</v>
       </c>
       <c r="K49" s="3" t="n">
         <v>665.8920000000001</v>
@@ -3659,16 +3661,16 @@
         <v>0</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>201.843</v>
+        <v>11.363</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>671.4880000000001</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3" t="n">
         <v>212.18</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>471.255</v>
+        <v>72.65300000000001</v>
       </c>
       <c r="K61" s="3" t="n">
         <v>77.56100000000001</v>
@@ -3721,16 +3723,18 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>319.553</v>
-      </c>
-      <c r="H62" s="3" t="n">
-        <v>1878.916</v>
+        <v>129.073</v>
+      </c>
+      <c r="H62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I62" s="3" t="n">
         <v>4838.663</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>2757.784</v>
+        <v>2359.182</v>
       </c>
       <c r="K62" s="3" t="n">
         <v>1938.839</v>
@@ -5326,43 +5330,43 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.174226</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.175358</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.22411</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.741737</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>20.745</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>-5.285</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>139.327</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>145.395</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>141.5</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>157.213</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>154.04</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>162.351</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>0.15897</v>
@@ -8390,7 +8394,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -12042,7 +12046,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -13875,7 +13879,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -17533,7 +17541,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -23366,7 +23374,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -35882,7 +35890,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -37059,7 +37071,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E328" s="5" t="n">
         <v>0.174226</v>
       </c>

--- a/output/pdf_financials_xlsx/ACB.xlsx
+++ b/output/pdf_financials_xlsx/ACB.xlsx
@@ -981,13 +981,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.015025</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.009389</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.007854999999999999</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1875,13 +1875,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.31576</v>
+        <v>-0.330785</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.393489</v>
+        <v>-0.402878</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.823535</v>
+        <v>-1.83139</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-9.726077</v>
@@ -1979,13 +1979,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.315338</v>
+        <v>-0.330363</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.393057</v>
+        <v>-0.402446</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.823232</v>
+        <v>-1.831087</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-9.421281</v>
@@ -2953,34 +2953,34 @@
         <v>0.736</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.126</v>
+        <v>1.544</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>7.594</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>24.323</v>
+        <v>233.282</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>22.137</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>11.169</v>
+        <v>113.117</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>6.539</v>
+        <v>189.885</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>8.279999999999999</v>
+        <v>138.853</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>9.401999999999999</v>
+        <v>97.461</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.011215</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.01112</v>
+        <v>0.08111</v>
       </c>
     </row>
     <row r="49">
@@ -3005,18 +3005,16 @@
         <v>5.244</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>193.606</v>
-      </c>
-      <c r="H49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.126</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>7.594</v>
       </c>
       <c r="I49" s="3" t="n">
         <v>660.578</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>420.739</v>
+        <v>22.137</v>
       </c>
       <c r="K49" s="3" t="n">
         <v>665.8920000000001</v>
@@ -3661,16 +3659,16 @@
         <v>0</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>11.363</v>
+        <v>201.843</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0</v>
+        <v>671.4880000000001</v>
       </c>
       <c r="I61" s="3" t="n">
         <v>212.18</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>72.65300000000001</v>
+        <v>471.255</v>
       </c>
       <c r="K61" s="3" t="n">
         <v>77.56100000000001</v>
@@ -3723,18 +3721,16 @@
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>129.073</v>
-      </c>
-      <c r="H62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>319.553</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>1878.916</v>
       </c>
       <c r="I62" s="3" t="n">
         <v>4838.663</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>2359.182</v>
+        <v>2757.784</v>
       </c>
       <c r="K62" s="3" t="n">
         <v>1938.839</v>
@@ -8394,7 +8390,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -12046,7 +12042,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -17541,7 +17537,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -23374,7 +23370,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -95957,7 +95953,7 @@
       </c>
       <c r="D986" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E986" s="5" t="n">

--- a/output/pdf_financials_xlsx/ACB.xlsx
+++ b/output/pdf_financials_xlsx/ACB.xlsx
@@ -5722,34 +5722,34 @@
         <v>0</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>1.087</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>12.26</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>88.255</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>114.72</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>98.07599999999999</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>93.66</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>31.635</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>32.775</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.012604</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.014192</v>
       </c>
     </row>
     <row r="101">
@@ -37423,7 +37423,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -37512,7 +37516,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -40411,7 +40415,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -42782,7 +42786,11 @@
           <t>Depreciation of property, plant and equipment 10</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -42869,7 +42877,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -45163,7 +45171,11 @@
           <t>Depreciation of property, plant and equipment 11</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -45246,7 +45258,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -51978,7 +51990,11 @@
           <t>Depreciation of property, plant and equipment 9</t>
         </is>
       </c>
-      <c r="D497" t="inlineStr"/>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E497" t="inlineStr">
         <is>
           <t>-</t>
@@ -52069,7 +52085,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -53519,7 +53535,7 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">

--- a/output/pdf_financials_xlsx/ACB.xlsx
+++ b/output/pdf_financials_xlsx/ACB.xlsx
@@ -1231,7 +1231,7 @@
         <v>20.382</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-0.135964</v>
+        <v>-0.192488</v>
       </c>
     </row>
     <row r="17">
@@ -1256,10 +1256,10 @@
         <v>0.149</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>4.296</v>
+        <v>-4.296</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-8.099</v>
+        <v>8.1</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0</v>
@@ -1280,10 +1280,10 @@
         <v>-0.554</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-20.380409</v>
+        <v>-0.031295</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>-0</v>
+        <v>0.056524</v>
       </c>
     </row>
     <row r="18">
@@ -1478,19 +1478,19 @@
         <v>69.227</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-300.596</v>
+        <v>-300.74</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-3309.36</v>
+        <v>-3257.499</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>-695.0890000000001</v>
+        <v>-693.477</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-1717.979</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-205.138</v>
+        <v>-183.228</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>-57.083</v>
@@ -1917,7 +1917,7 @@
         <v>20.382</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.135964</v>
+        <v>-0.192488</v>
       </c>
     </row>
     <row r="28">
@@ -2021,7 +2021,7 @@
         <v>20.384984</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.13215</v>
+        <v>-0.188674</v>
       </c>
     </row>
     <row r="30">
@@ -2081,7 +2081,7 @@
         <v>6373.135578913143</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-38.59250519823377</v>
+        <v>-55.09952573417751</v>
       </c>
     </row>
     <row r="31">
@@ -2109,7 +2109,7 @@
         <v>-24.88415199258572</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>10.47383803636552</v>
+        <v>10.4751312624473</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -2130,10 +2130,10 @@
         <v>-0.961188125683155</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>99.99219409282701</v>
+        <v>0.1535423412815229</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0</v>
+        <v>-29.36494742529405</v>
       </c>
     </row>
     <row r="32">
@@ -2384,7 +2384,7 @@
         <v>2.312</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>6.665</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>0</v>
@@ -2592,7 +2592,7 @@
         <v>5.63</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>6.665</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>0</v>
@@ -4171,10 +4171,10 @@
         <v>0</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.037495</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.01813</v>
       </c>
     </row>
     <row r="71">
@@ -4223,10 +4223,10 @@
         <v>0</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.037495</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.01813</v>
       </c>
     </row>
     <row r="72">
@@ -4431,10 +4431,10 @@
         <v>64.37</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.036184</v>
+        <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.015068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4716,15 +4716,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O80" s="3" t="n">
+        <v>6.160952100836194e-05</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0.03542177902124134</v>
       </c>
     </row>
     <row r="81">
@@ -5676,28 +5672,28 @@
         <v>69.227</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>-297.924</v>
+        <v>-300.74</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>-3309.36</v>
+        <v>-3257.499</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>-695.0890000000001</v>
+        <v>-693.477</v>
       </c>
       <c r="L99" s="3" t="n">
         <v>-1717.979</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>-206.295</v>
+        <v>-183.228</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>-57.083</v>
+        <v>-59.045</v>
       </c>
       <c r="O99" s="3" t="n">
-        <v>0.02705</v>
+        <v>0.001591</v>
       </c>
       <c r="P99" s="3" t="n">
-        <v>-0.058619</v>
+        <v>-0.135964</v>
       </c>
     </row>
     <row r="100">
@@ -5759,25 +5755,25 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.006753</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.00439</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>-0.00253</v>
+        <v>-0.247053</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>-1.680506</v>
+        <v>-0.368659</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>-0.081</v>
+        <v>0.542</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>-0.654</v>
+        <v>-1.617</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>-5.887</v>
+        <v>-12.357</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>0</v>
@@ -6236,31 +6232,31 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.113724</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.622</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>3.459</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>9.734999999999999</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>22.798</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>18.359</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>30.493</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>30.082</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>15.866</v>
       </c>
       <c r="N110" s="3" t="n">
         <v>0</v>
@@ -6279,7 +6275,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00091</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -6508,13 +6504,13 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>46.975</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>90.843</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>18.064</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
@@ -6526,7 +6522,7 @@
         <v>0</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.005488</v>
       </c>
       <c r="P115" s="3" t="n">
         <v>0</v>
@@ -7513,7 +7509,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00091</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -10141,7 +10137,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -27334,7 +27334,11 @@
           <t>Impairment of intangible assets and goodwill</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -37160,11 +37164,7 @@
           <t>Net income (loss) from continuing operations</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -38851,7 +38851,11 @@
           <t>Proceeds from disposal of marketable securities</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -40767,7 +40771,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
           <t>-</t>
@@ -42531,7 +42539,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -45790,7 +45802,11 @@
           <t>Accrued interest and accretion expense 16</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -47558,7 +47574,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
           <t>-</t>
@@ -47819,7 +47839,11 @@
           <t>Proceeds from disposal of marketable securities 7</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
           <t>-</t>
@@ -49142,7 +49166,11 @@
           <t>Accrued interest and accretion expense 16, 17</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr"/>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E465" t="inlineStr">
         <is>
           <t>-</t>
@@ -50645,7 +50673,11 @@
           <t>Accrued interest and accretion expense 15, 16</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E482" t="inlineStr">
         <is>
           <t>-</t>
@@ -52447,7 +52479,11 @@
           <t>Accrued interest and accretion expense 13, 14</t>
         </is>
       </c>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
           <t>-</t>
@@ -52714,7 +52750,11 @@
           <t>Proceeds from disposal of marketable securities 5</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
           <t>-</t>
@@ -54265,7 +54305,11 @@
           <t>Accrued interest and accretion expense</t>
         </is>
       </c>
-      <c r="D522" t="inlineStr"/>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E522" t="inlineStr">
         <is>
           <t>-</t>
@@ -54354,7 +54398,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D523" t="inlineStr"/>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E523" t="inlineStr">
         <is>
           <t>-</t>
@@ -57489,7 +57537,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D558" t="inlineStr"/>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E558" t="inlineStr">
         <is>
           <t>-</t>
@@ -59554,7 +59606,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D581" t="inlineStr"/>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E581" t="inlineStr">
         <is>
           <t>-</t>
@@ -60549,7 +60605,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D592" t="inlineStr"/>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E592" t="inlineStr">
         <is>
           <t>-</t>
@@ -62181,7 +62241,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D610" t="inlineStr"/>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E610" t="inlineStr">
         <is>
           <t>-</t>
@@ -63386,7 +63450,11 @@
           <t>HST/GST recoverable</t>
         </is>
       </c>
-      <c r="D623" t="inlineStr"/>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E623" s="5" t="n">
         <v>-0.006753</v>
       </c>
@@ -63475,7 +63543,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D624" t="inlineStr"/>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E624" s="5" t="n">
         <v>-0.00091</v>
       </c>
@@ -65916,7 +65988,11 @@
           <t>Income (loss) before income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D651" t="inlineStr"/>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E651" t="inlineStr">
         <is>
           <t>-</t>
@@ -66183,7 +66259,11 @@
           <t>Income tax recovery (expense) total</t>
         </is>
       </c>
-      <c r="D654" t="inlineStr"/>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E654" t="inlineStr">
         <is>
           <t>-</t>
@@ -75952,7 +76032,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D763" t="inlineStr"/>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E763" t="inlineStr">
         <is>
           <t>-</t>
@@ -76213,7 +76297,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D766" t="inlineStr"/>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E766" t="inlineStr">
         <is>
           <t>-</t>
@@ -83171,7 +83259,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D844" t="inlineStr"/>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E844" t="inlineStr">
         <is>
           <t>-</t>
@@ -87117,7 +87209,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D888" t="inlineStr"/>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E888" t="inlineStr">
         <is>
           <t>-</t>
